--- a/tests/appium/reports/appium-report.xlsx
+++ b/tests/appium/reports/appium-report.xlsx
@@ -494,7 +494,7 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -543,7 +543,7 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="s">
         <v>16</v>
